--- a/results/result_evaluation_logs/F_URI_Retrieval_Filtering_One_Agent.xlsx
+++ b/results/result_evaluation_logs/F_URI_Retrieval_Filtering_One_Agent.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,11 +544,6 @@
           <t>Result String</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Langfuse Trace ID</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -626,11 +621,6 @@
 </t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>cd789e3f-ad1f-41bb-8214-f91025094499</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -706,11 +696,6 @@
 wd:Q20992419 wd:P4794 "June" .
 wd:Q20992419 wd:P527 wd:Q17516 .
 </t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>486db381-102e-4320-a96e-84fc7338412d</t>
         </is>
       </c>
     </row>
@@ -789,11 +774,6 @@
 wd:Q466774 wd:P108 wd:Q273626 .
 wd:Q466774 wd:P1027 wd:Q370496 .
 </t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>cd8134a9-0341-4a8f-9645-e40b1681f163</t>
         </is>
       </c>
     </row>
@@ -877,11 +857,6 @@
 </t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>91e570a4-b8a0-419e-9d0e-02daa4fad408</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -956,11 +931,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q36771 wd:P19 wd:Q29999 .
 </t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>20d0e4b0-44a9-4c30-95a2-76c013518149</t>
         </is>
       </c>
     </row>
@@ -1039,11 +1009,6 @@
 </t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>d8649429-bdda-4420-a7ec-f5c66afc81de</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1120,11 +1085,6 @@
 </t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>ec2ec44c-d99c-4106-9611-1c776fcdf227</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1201,11 +1161,6 @@
 wd:Q2601034 wd:P264 wd:Q3939773 .
 wd:Q2601034 wd:P750 wd:Q3939773 .
 </t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>9e5f169c-17de-405f-9cb7-7ecce12ca6eb</t>
         </is>
       </c>
     </row>
@@ -1287,11 +1242,6 @@
 </t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>541b7b7a-6ad0-499a-bd5a-6bfbf54dcc6e</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1369,11 +1319,6 @@
 </t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>dd9c9441-fca9-478e-b930-27921f5cf5c4</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1451,11 +1396,6 @@
 </t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>5d22b654-1f99-469f-b681-76f9b3cb65db</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1533,11 +1473,6 @@
 </t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>c49f42ca-65d4-4bef-8e56-1a9708188f50</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1615,11 +1550,6 @@
 </t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>20b749e3-88a0-41bf-bdfb-fc185782d21d</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1698,11 +1628,6 @@
 </t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>12f18e2b-91a4-40c3-9607-6495e16adc4a</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1779,11 +1704,6 @@
 </t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>efbbfe8d-0591-472e-a203-c90910c4a26c</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1861,11 +1781,6 @@
 </t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>ca41b6c6-a69d-410c-a22b-5651898914b4</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1944,11 +1859,6 @@
 </t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>aadb1ef9-4c4c-4bc7-88b7-3f498974d11e</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2027,11 +1937,6 @@
 </t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>f02c9016-9315-4d88-9f8e-f33039ac82d0</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2106,11 +2011,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q20671544 wd:P527 wd:Q27914 .
 </t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>dc429eaa-511f-48f1-b6bb-fab700ec047c</t>
         </is>
       </c>
     </row>
@@ -2194,11 +2094,6 @@
 </t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>f75b9c29-bc97-45ba-92dd-c0417a76208d</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2275,11 +2170,6 @@
 </t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>20479f78-6275-4197-be42-9ad1b8204f1d</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2358,11 +2248,6 @@
 </t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>dd1c8fc9-d66f-4baf-8082-3df1561b188f</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2440,11 +2325,6 @@
 </t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>bee12c89-0670-41ab-af45-d8ab8cc34d59</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2521,11 +2401,6 @@
 wd:Q5554167 wd:P750 wd:Q520445 .
 wd:Q5554167 wd:P449 wd:Q220072 .
 </t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>5fd456de-f72f-44f3-832a-acb2fc7fba6b</t>
         </is>
       </c>
     </row>
@@ -2613,11 +2488,6 @@
 </t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>e6e2e719-6d28-43b4-b600-eb737947867f</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2695,11 +2565,6 @@
 </t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>98f9f749-aa3c-4fd0-8171-6cb7e11787f8</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2777,11 +2642,6 @@
 </t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>97179905-011f-4da2-84ec-08d28bbbb64a</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2860,11 +2720,6 @@
 </t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>6872b385-73e8-4f72-844d-71a5de0f4a7a</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2910,10 +2765,10 @@
         <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
@@ -2941,11 +2796,6 @@
 wd:Q8083051 wd:P361 wd:Q1840968 .
 wd:Q8083051 wd:P361 wd:Q1840968 .
 </t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>15e1038a-980a-41ff-b46e-63e14ddb5ba8</t>
         </is>
       </c>
     </row>
@@ -3027,11 +2877,6 @@
 </t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>c1131e6c-69d1-4cad-b120-171cadaf8616</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3077,10 +2922,10 @@
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
         <v>2</v>
@@ -3107,11 +2952,6 @@
 wd:Q64876878 wd:P161 wd:Q65090308 .
 wd:Q262170 wd:P725 wd:Q64876878 .
 </t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>1538a5f8-2ad1-4b20-85e3-d609c6a7262b</t>
         </is>
       </c>
     </row>
@@ -3193,11 +3033,6 @@
 </t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>1175bd33-bc62-4b56-9e68-3ab0df2ae463</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3276,11 +3111,6 @@
 </t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>e6fda46b-6b39-41de-bb80-b3714d96dbe5</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3357,11 +3187,6 @@
 </t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>c0cf7bbe-5032-4391-ac4a-b1d2bd7c89dc</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3438,11 +3263,6 @@
 </t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>5f4bf757-3591-4ba5-a42e-2ac19137bc02</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3519,11 +3339,6 @@
 wd:Q2616869 wd:P31 wd:Q47461344 .
 wd:Q2616869 wd:P275 wd:Q19652 .
 </t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>5e7545d2-1237-4a25-b30e-938e0e0aede3</t>
         </is>
       </c>
     </row>
@@ -3605,11 +3420,6 @@
 </t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>900c8973-7a3a-4933-a514-c406e8f0e30e</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3688,11 +3498,6 @@
 </t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>ca804ed0-f74c-4c85-bb6b-7f73432dee85</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3769,11 +3574,6 @@
 </t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>a955d858-d043-471d-b8fa-e90f4d29aaf6</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3849,11 +3649,6 @@
 wd:Q47554 wd:P1376 wd:Q54153 .
 wd:Q47554 wd:P706 wd:Q1261531 .
 </t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>eef9723d-6ac3-4a82-9473-232c90868a85</t>
         </is>
       </c>
     </row>
@@ -3935,11 +3730,6 @@
 </t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>f96f853e-922b-497a-8d1f-efd37300bcf4</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4017,11 +3807,6 @@
 </t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>80fefbfc-5fd3-4f6e-b906-b57d5cf77e8e</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4098,11 +3883,6 @@
 </t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>2bda08b5-a323-4a8e-83cc-c2932b87fdc4</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4180,11 +3960,6 @@
 </t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>9ca22bf4-233f-4060-8a21-cfdb947acae9</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4263,11 +4038,6 @@
 </t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>634aa049-0214-46dc-a4be-51779252ee0b</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4344,11 +4114,6 @@
 </t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>8a734389-b4ad-487b-81b0-5d9e0e0354d8</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4423,11 +4188,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q977911 wd:P47 wd:Q979352 .
 </t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>1b16008e-c629-4f90-b56c-0ad8936ad8be</t>
         </is>
       </c>
     </row>
@@ -4509,11 +4269,6 @@
 </t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>518d5c14-56e5-4526-9331-a85184197d01</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4559,10 +4314,10 @@
         <v>3</v>
       </c>
       <c r="O50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q50" t="n">
         <v>3</v>
@@ -4592,11 +4347,6 @@
 </t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>cc8ff7ed-fb21-4896-a538-d846f8fa7bde</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4671,11 +4421,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q2362697 wd:P556 wd:Q503601 .
 </t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>333fb9e3-8c3a-4007-a586-0b1d9bb9819a</t>
         </is>
       </c>
     </row>

--- a/results/result_evaluation_logs/F_URI_Retrieval_Filtering_One_Agent.xlsx
+++ b/results/result_evaluation_logs/F_URI_Retrieval_Filtering_One_Agent.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W51"/>
+  <dimension ref="A1:X51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,19 +544,24 @@
           <t>Result String</t>
         </is>
       </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Langfuse Trace ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
@@ -580,19 +585,19 @@
         <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>2</v>
@@ -616,9 +621,14 @@
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q25095540 wd:P1433 wd:Q1516254 .
-wd:Q25095540 wd:P50 wd:Q364841 .
-</t>
+wd:Q25095540 wd:P175 wd:Q364841 .
+wd:Q25095540 wd:P2579 wd:Q1516254 .
+</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>6b1b699f-90c0-4712-a878-2246e80a5ea6</t>
         </is>
       </c>
     </row>
@@ -678,7 +688,7 @@
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
         <v>3</v>
@@ -687,15 +697,20 @@
         <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q20992419 wd:P4794 "June" .
-wd:Q20992419 wd:P527 wd:Q17516 .
-</t>
+wd:Q20992419 wd:P31 wd:Q17516 .
+wd:Q20992419 wd:P361 wd:Q120 .
+</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>bf6e1a08-291d-4dbc-9071-ca5a323ba033</t>
         </is>
       </c>
     </row>
@@ -704,13 +719,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>5</v>
@@ -719,13 +734,13 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -734,19 +749,19 @@
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
@@ -758,22 +773,27 @@
         <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U4" t="n">
         <v>6</v>
       </c>
       <c r="V4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q466774 wd:P106 wd:Q395 .
 wd:Q466774 wd:P108 wd:Q273626 .
-wd:Q466774 wd:P1027 wd:Q370496 .
-</t>
+wd:Q466774 wd:P184 wd:Q370496 .
+wd:Q142 wd:P194 wd:Q632552 .
+</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3857f22e-d2ad-4064-9aa6-37c72852f565</t>
         </is>
       </c>
     </row>
@@ -794,10 +814,10 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -815,46 +835,49 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
         <v>6</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5" t="n">
         <v>7</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q72697912 wd:P31 wd:Q11424 .
-wd:Q72697912 wd:P840 wd:Q1993848 .
-wd:Q72697912 wd:P840 wd:Q81725 .
-wd:Q72697912 wd:P577 wd:2020 .
-wd:Q72697912 wd:P577 &lt;http://www.wikidata.org/entity/Q4557532&gt; .
-wd:Q72697912 wd:P162 wd:Q258 .
-</t>
+wd:Q72697912 wd:P361 wd:Q11424 .
+wd:Q72697912 wd:P921 wd:Q1993848 .
+wd:Q72697912 wd:P750 wd:Q55970 .
+wd:Q81725 wd:P131 wd:Q258 .
+</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>af78bb7d-d2b6-4962-ad94-090641b8d3bc</t>
         </is>
       </c>
     </row>
@@ -863,13 +886,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -893,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -929,8 +952,13 @@
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q36771 wd:P19 wd:Q29999 .
-</t>
+wd:Q36771 wd:P27 wd:Q29999 .
+</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3dc5cff9-7119-4517-8c60-873b6743b699</t>
         </is>
       </c>
     </row>
@@ -942,16 +970,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -963,7 +991,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -972,41 +1000,48 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
         <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
         <v>4</v>
       </c>
       <c r="V7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+wd:Q506252 wd:P31 wd:Q279014 .
+wd:Q506252 wd:P366 wd:Q192786 .
 wd:Q506252 wd:P366 wd:Q177 .
 </t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>ba3a19c6-ef41-4eef-abd2-3c5fff940f2e</t>
         </is>
       </c>
     </row>
@@ -1015,19 +1050,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -1039,50 +1074,56 @@
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
         <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
         <v>3</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q2226643 wd:P138 wd:Q28937 .
-</t>
+wd:Q2226643 wd:P31 wd:Q65943 .
+</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>00f36009-93ab-4dcb-8d5d-0872028d04e6</t>
         </is>
       </c>
     </row>
@@ -1103,10 +1144,10 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
@@ -1115,7 +1156,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
         <v>6</v>
@@ -1136,31 +1177,37 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
         <v>6</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U9" t="n">
         <v>7</v>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q2808 wd:P175 wd:Q2601034 .
-wd:Q2601034 wd:P264 wd:Q3939773 .
+wd:Q2601034 wd:P162 wd:Q2338060 .
+wd:Q2601034 wd:P674 wd:Q2808 .
 wd:Q2601034 wd:P750 wd:Q3939773 .
-</t>
+wd:Q2601034 wd:P31 wd:Q11399 .
+</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>19535bd5-5f33-4676-bcff-d3b8739c96ec</t>
         </is>
       </c>
     </row>
@@ -1169,22 +1216,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
         <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>3</v>
@@ -1193,34 +1240,34 @@
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
         <v>7</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
         <v>7</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
         <v>7</v>
@@ -1236,10 +1283,16 @@
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q6782514 wd:P131 wd:Q1364658 .
+wd:Q6782514 wd:P421 wd:Q6760 .
 wd:Q924 wd:P37 wd:Q7838 .
+wd:Q924 wd:P530 wd:Q423 .
 wd:Q924 wd:P1906 wd:Q7241291 .
-wd:Q423 wd:P131 wd:Q1773949 .
-</t>
+</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>ded1a5c4-0d28-4c64-b0b2-a79f778d5b9c</t>
         </is>
       </c>
     </row>
@@ -1248,75 +1301,82 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
         <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
         <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U11" t="n">
         <v>6</v>
       </c>
       <c r="V11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+wd:Q85563 wd:P27 wd:Q183 .
 wd:Q85563 wd:P26 wd:Q58284 .
 wd:Q85563 wd:P3373 wd:Q91204 .
-</t>
+wd:Q592 wd:P5008 wd:Q8661954 .
+</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>d9dc1273-dd1f-48d4-92c3-37b9489dedbc</t>
         </is>
       </c>
     </row>
@@ -1325,19 +1385,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -1349,51 +1409,58 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
         <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
         <v>5</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U12" t="n">
         <v>6</v>
       </c>
       <c r="V12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q5395743 wd:P1433 wd:Q1321 .
-wd:Q5395743 wd:P17 wd:Q96 .
-</t>
+wd:Q5395743 wd:P407 wd:Q1321 .
+wd:Q5395743 wd:P37 wd:Q1321 .
+wd:Q5395743 wd:P101 wd:Q735 .
+wd:Q5395743 wd:P361 wd:Q806208 .
+</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>e6d5b8b0-d2d7-4748-b4b3-396e55af8a2f</t>
         </is>
       </c>
     </row>
@@ -1402,13 +1469,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
@@ -1417,7 +1484,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
@@ -1432,19 +1499,19 @@
         <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
         <v>2</v>
@@ -1453,7 +1520,7 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
         <v>3</v>
@@ -1468,9 +1535,14 @@
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q271108 wd:P533 wd:Q516760 .
-wd:Q516760 wd:P2348 wd:Q1605654 .
-</t>
+wd:Q516760 wd:P276 wd:Q1605654 .
+wd:Q516760 wd:P361 wd:Q271108 .
+</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>727feee6-8b4e-4d19-a425-4f4d1503fcee</t>
         </is>
       </c>
     </row>
@@ -1479,22 +1551,22 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
         <v>2</v>
@@ -1503,34 +1575,34 @@
         <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
         <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
         <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
         <v>3</v>
@@ -1545,9 +1617,15 @@
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q7992209 wd:P4661 wd:Q3561541 .
-wd:Q3561541 wd:P1535 wd:Q5364109 .
-</t>
+wd:Q3561541 wd:P4661 wd:Q7992209 .
+wd:Q7992209 wd:P4792 wd:Q5364109 .
+wd:Q5364109 wd:P200 wd:Q3561541 .
+</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>b2e98905-2dbb-40be-94f4-7ba02e1e5686</t>
         </is>
       </c>
     </row>
@@ -1556,13 +1634,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>4</v>
@@ -1571,7 +1649,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -1580,37 +1658,37 @@
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
         <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
         <v>4</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
         <v>5</v>
@@ -1622,10 +1700,15 @@
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q42916999 wd:P1346 wd:Q82955 .
-wd:Q568973 wd:P541 wd:Q11696 .
-wd:Q28221935 wd:P102 wd:Q82955 .
-</t>
+wd:Q42916999 wd:P361 wd:Q568973 .
+wd:Q42916999 wd:P31 wd:Q28221935 .
+wd:Q42916999 wd:P361 wd:Q48845659 .
+</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>df74f6fd-1971-4de0-9ce7-1ada54706040</t>
         </is>
       </c>
     </row>
@@ -1704,6 +1787,11 @@
 </t>
         </is>
       </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>dc748e50-c7ca-41cc-abaa-3d1903f1fb8b</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1740,19 +1828,19 @@
         <v>3</v>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
         <v>2</v>
@@ -1777,8 +1865,13 @@
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q7044514 wd:P175 wd:Q234199 .
-wd:Q7044514 wd:P31 wd:Q46046 .
-</t>
+wd:Q7044514 wd:P361 wd:Q46046 .
+</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>93e52b6d-6900-43f7-ac64-20d1ad0fdd15</t>
         </is>
       </c>
     </row>
@@ -1787,13 +1880,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
@@ -1817,19 +1910,19 @@
         <v>3</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
         <v>3</v>
@@ -1853,10 +1946,15 @@
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+wd:Q607380 wd:P5588 wd:Q782 .
 wd:Q607380 wd:P183 wd:Q664 .
-wd:Q607380 wd:P5588 wd:Q782 .
-wd:Q607380 wd:P186 wd:Q6933370 .
-</t>
+wd:Q607380 wd:P1672 wd:Q6933370 .
+</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>ab0925b9-f6d2-4ae2-bdeb-09e456fac42a</t>
         </is>
       </c>
     </row>
@@ -1865,28 +1963,28 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
         <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -1895,19 +1993,19 @@
         <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
         <v>3</v>
@@ -1919,22 +2017,28 @@
         <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U19" t="n">
         <v>5</v>
       </c>
       <c r="V19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q5686841 wd:P179 wd:Q308864 .
-wd:Q5686841 wd:P179 wd:Q928828 .
-wd:Q5686841 wd:P179 wd:Q1282219 .
-</t>
+wd:Q5686841 wd:P150 wd:Q308864 .
+wd:Q794 wd:P150 wd:Q308864 .
+wd:Q308864 wd:P150 wd:Q1282219 .
+wd:Q928828 wd:P150 wd:Q794 .
+</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>b32a6862-2213-4ff1-84c4-09c9a657e4ee</t>
         </is>
       </c>
     </row>
@@ -2013,28 +2117,33 @@
 </t>
         </is>
       </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>3a6a2479-a394-43ca-9411-367ce968b5d6</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
         <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>2</v>
@@ -2043,55 +2152,59 @@
         <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
         <v>7</v>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
         <v>7</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U21" t="n">
         <v>8</v>
       </c>
       <c r="V21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q3048624 wd:P569 [] .
+wd:Q3048624 wd:P106 wd:Q82955 .
+wd:Q16 wd:P2238 wd:Q81056 .
+wd:Q16 wd:P237 wd:Q41549 .
+wd:Q16 wd:P122 wd:Q41614 .
 wd:Q3048624 wd:P1412 wd:Q1860 .
-wd:Q16 wd:P2238 wd:Q81056 .
-wd:Q16 wd:P122 wd:Q18340522 .
-wd:Q16 wd:P36 wd:Q1003 .
-wd:Q41549 wd:P361 wd:Q16 .
-</t>
+</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>0e235eed-277d-4832-addc-db852a1732c7</t>
         </is>
       </c>
     </row>
@@ -2170,19 +2283,24 @@
 </t>
         </is>
       </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>82c35816-10ef-4ab2-8ac8-b0abc137baee</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
@@ -2206,19 +2324,19 @@
         <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
         <v>3</v>
@@ -2242,10 +2360,15 @@
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q18036690 wd:P1057 wd:Q430258 .
+wd:Q18036690 wd:P706 wd:Q430258 .
 wd:Q18036690 wd:P1479 wd:Q12174 .
 wd:Q18036690 wd:P703 wd:Q15978631 .
 </t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>1138b29d-589e-47ed-b710-76c592c72e40</t>
         </is>
       </c>
     </row>
@@ -2254,13 +2377,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -2284,19 +2407,19 @@
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" t="n">
         <v>2</v>
@@ -2320,9 +2443,14 @@
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q188197 wd:P1346 wd:Q1856183 .
-wd:Q188197 wd:P1346 wd:Q674962 .
-</t>
+wd:Q188197 wd:P2522 wd:Q1856183 .
+wd:Q188197 wd:P2522 wd:Q674962 .
+</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>3a4d3591-8a5e-4960-a9dd-862d14c9b1c3</t>
         </is>
       </c>
     </row>
@@ -2397,10 +2525,15 @@
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q5554167 wd:P287 wd:Q16239205 .
+wd:Q5554167 wd:P86 wd:Q16239205 .
 wd:Q5554167 wd:P750 wd:Q520445 .
-wd:Q5554167 wd:P449 wd:Q220072 .
-</t>
+wd:Q5554167 wd:P1408 wd:Q220072 .
+</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>ed1130a0-ab38-4273-9cf7-f6888b4f8879</t>
         </is>
       </c>
     </row>
@@ -2409,19 +2542,19 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
         <v>7</v>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -2433,43 +2566,43 @@
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
         <v>4</v>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
         <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
         <v>3</v>
       </c>
       <c r="Q26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R26" t="n">
         <v>7</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U26" t="n">
         <v>7</v>
       </c>
       <c r="V26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -2479,13 +2612,15 @@
 wd:Q62066211 wd:P533 wd:Q62066751 .
 wd:Q62066211 wd:P739 wd:Q486396 .
 wd:Q62066211 wd:P739 wd:Q11244 .
+wd:Q62066211 wd:P828 wd:Q486296 .
 wd:Q62066211 wd:P828 wd:Q698752 .
-wd:Q62066211 wd:P533 wd:Q5 .
-wd:Q62066211 wd:P421 wd:Q6760 .
-wd:Q62066211 wd:P2522 wd:Q1323212 .
-wd:Q62066211 wd:P533 wd:Q5 .
-wd:Q62066211 wd:P3342 wd:Q698752 .
-</t>
+wd:Q62066211 wd:P793 wd:Q62066211 .
+</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>7d27acdf-7767-490a-9608-c471d94372f3</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2641,7 @@
         <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>2</v>
@@ -2524,45 +2659,51 @@
         <v>4</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
         <v>4</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U27" t="n">
         <v>5</v>
       </c>
       <c r="V27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q2094579 wd:P58 wd:Q5546527 .
-wd:Q5546527 wd:P138 wd:Q37326 .
-</t>
+wd:Q2094579 wd:P162 wd:Q5546527 .
+wd:Q2094579 wd:P162 wd:Q827379 .
+wd:Q5546527 wd:P735 "George" .
+</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>c8ab41fd-b4f5-4092-85ce-9f891aaebd1b</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2712,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
         <v>2</v>
@@ -2601,7 +2742,7 @@
         <v>2</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
         <v>2</v>
@@ -2636,10 +2777,15 @@
       <c r="W28" t="inlineStr">
         <is>
           <t xml:space="preserve">
-@prefix wd: &lt;http://www.wikidata.org/entity/&gt;.
-wd:Q22082365 wd:P131 wd:Q965 .
+@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+wd:Q22082365 wd:P17 wd:Q965 .
 wd:Q965 wd:P463 wd:Q47543 .
 </t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>10c3c05e-4e78-4541-aaa2-8787524be0c6</t>
         </is>
       </c>
     </row>
@@ -2648,22 +2794,22 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
         <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
@@ -2672,52 +2818,58 @@
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
         <v>3</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
         <v>4</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U29" t="n">
         <v>5</v>
       </c>
       <c r="V29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q16926803 wd:P527 wd:Q6811747 .
-wd:Q16926803 wd:P527 wd:Q6762533 .
-wd:Q16926803 wd:P127 wd:Q8062829 .
-</t>
+wd:Q16926803 wd:P3438 wd:Q8062829 .
+wd:Q8062829 wd:P137 wd:Q2060470 .
+wd:Q16926803 wd:P609 wd:Q6811747 .
+wd:Q16926803 wd:P609 wd:Q6762533 .
+</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>06cc7e09-7c0d-44bf-8ced-b2c134bc48ee</t>
         </is>
       </c>
     </row>
@@ -2729,16 +2881,16 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -2771,31 +2923,37 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
         <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U30" t="n">
         <v>5</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q8083051 wd:P131 wd:Q1840968 .
-wd:Q8083051 wd:P361 wd:Q1840968 .
-wd:Q8083051 wd:P361 wd:Q1840968 .
-</t>
+wd:Q8083051 wd:P131 wd:Q36 .
+wd:Q8083051 wd:P276 wd:Q6723 .
+wd:Q8083051 wd:P276 wd:Q6655 .
+</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>63dec11d-abeb-46ea-bde7-1b7099c470e9</t>
         </is>
       </c>
     </row>
@@ -2804,13 +2962,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
@@ -2819,7 +2977,7 @@
         <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
@@ -2849,7 +3007,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
         <v>3</v>
@@ -2858,7 +3016,7 @@
         <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U31" t="n">
         <v>4</v>
@@ -2871,10 +3029,15 @@
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q14707624 wd:P1408 wd:Q304801 .
-wd:Q14707624 wd:P131 wd:Q60 .
-wd:Q14707624 wd:P131 wd:Q1384 .
-wd:Q14707624 wd:P131 wd:Q30 .
-</t>
+wd:Q14707624 wd:P131 wd:Q304801 .
+wd:Q304801 wd:P131 wd:Q1384 .
+wd:Q1384 wd:P131 wd:Q30 .
+</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>63306ae5-9065-4da5-81d0-39c350ba3e64</t>
         </is>
       </c>
     </row>
@@ -2883,10 +3046,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
@@ -2898,7 +3061,7 @@
         <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
@@ -2922,10 +3085,10 @@
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q32" t="n">
         <v>2</v>
@@ -2934,7 +3097,7 @@
         <v>2</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T32" t="n">
         <v>3</v>
@@ -2949,9 +3112,14 @@
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q64876878 wd:P161 wd:Q65090308 .
-wd:Q262170 wd:P725 wd:Q64876878 .
-</t>
+wd:Q64876878 wd:P725 wd:Q262170 .
+wd:Q64876878 wd:P674 wd:Q65090308 .
+</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>cf5a82c9-073d-4d82-81cd-9c4c2cbc270c</t>
         </is>
       </c>
     </row>
@@ -2963,7 +3131,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
         <v>2</v>
@@ -2972,65 +3140,72 @@
         <v>6</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H33" t="n">
         <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
         <v>6</v>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P33" t="n">
         <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
         <v>6</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U33" t="n">
         <v>7</v>
       </c>
       <c r="V33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q1240173 wd:P131 wd:Q1088790 .
-wd:Q1240173 wd:P131 wd:Q190518 .
-wd:Q1240173 wd:P131 wd:Q28 .
-wd:Q1240173 wd:P149 wd:Q2722661 .
-</t>
+wd:Q1240173 wd:P159 wd:Q1088790 .
+wd:Q1240173 wd:P149 wd:Q46261 .
+wd:Q46261 wd:P2670 wd:Q2722661 .
+wd:Q2722661 wd:P2670 wd:Q202763 .
+wd:Q1088790 wd:P2670 wd:Q28 .
+wd:Q190518 wd:P2670 wd:Q28 .
+</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>47f41c1e-00e7-46b2-8109-fae0279ade89</t>
         </is>
       </c>
     </row>
@@ -3039,13 +3214,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
         <v>3</v>
@@ -3090,7 +3265,7 @@
         <v>3</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T34" t="n">
         <v>4</v>
@@ -3099,16 +3274,21 @@
         <v>4</v>
       </c>
       <c r="V34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q822946 wd:P136 wd:Q1427016 .
 wd:Q822946 wd:P161 wd:Q1366759 .
-wd:Q822946 wd:P2408 wd:Q2644 .
-</t>
+wd:Q822946 wd:P2408 "1968" .
+wd:Q822946 wd:P136 wd:Q1427015 .
+</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>36143871-55ee-4a75-9e71-e519dbfd06cd</t>
         </is>
       </c>
     </row>
@@ -3187,6 +3367,11 @@
 </t>
         </is>
       </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>628ecdf5-4838-473b-8a7f-7e46a68dc9fa</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3226,16 +3411,16 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
@@ -3259,8 +3444,13 @@
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q1490434 wd:P361 wd:Q41298 .
-</t>
+wd:Q1490434 wd:P1433 wd:Q183 .
+</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>5e2b1b50-5bb3-49b3-b400-b2f484aad0e4</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3510,7 @@
         <v>3</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
         <v>4</v>
@@ -3329,16 +3519,21 @@
         <v>4</v>
       </c>
       <c r="V37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q2616869 wd:P1433 wd:Q1126800 .
-wd:Q2616869 wd:P31 wd:Q47461344 .
-wd:Q2616869 wd:P275 wd:Q19652 .
-</t>
+wd:Q2616869 wd:P31 wd:Q132311 .
+wd:Q2616869 wd:P5777 wd:Q19652 .
+</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>1c8ea7c0-a3f3-42ff-8782-6eeb0f6aea70</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3554,7 @@
         <v>4</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -3371,7 +3566,7 @@
         <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>4</v>
@@ -3392,34 +3587,38 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
         <v>4</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U38" t="n">
         <v>5</v>
       </c>
       <c r="V38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q6803534 wd:P31 wd:Q1320721 .
 wd:Q6803534 wd:P131 wd:Q1084560 .
 wd:Q6803534 wd:P131 wd:Q1247390 .
 wd:Q6803534 wd:P131 wd:Q145 .
 </t>
         </is>
       </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>39ea4b59-e227-417f-b4f9-b7b9a4eaf240</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3429,73 +3628,86 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>2</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>2</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
         <v>3</v>
       </c>
       <c r="V39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-@prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q907827 wd:P31 wd:Q907827 .
-wd:Q907827 wd:P361 wd:Q183 .
-wd:Q907827 wd:P1546 "Workers of the world, unite!" .
-</t>
+          <t xml:space="preserve">Error: Recursion limit of 70 reached without hitting a stop condition. You can increase the limit by setting the `recursion_limit` config key.
+For troubleshooting, visit: https://python.langchain.com/docs/troubleshooting/errors/GRAPH_RECURSION_LIMIT
+Traceback:
+Traceback (most recent call last):
+  File "/home/mlautenb/CIExMAS/./results/F_URI_Retrieval_Filtering/One_Agent/slurm/agent_system.py", line 71, in &lt;module&gt;
+    response = graph.invoke({"text": text, "messages": [], "instruction": "", "debug": False},
+               ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langgraph/pregel/__init__.py", line 2683, in invoke
+    for chunk in self.stream(
+  File "/home/mlautenb/miniconda3/envs/CIExMAS/lib/python3.11/site-packages/langgraph/pregel/__init__.py", line 2351, in stream
+    raise GraphRecursionError(msg)
+langgraph.errors.GraphRecursionError: Recursion limit of 70 reached without hitting a stop condition. You can increase the limit by setting the `recursion_limit` config key.
+For troubleshooting, visit: https://python.langchain.com/docs/troubleshooting/errors/GRAPH_RECURSION_LIMIT
+</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>9868a4e1-1fe5-4e14-901b-3c1a4cf9b6b4</t>
         </is>
       </c>
     </row>
@@ -3507,10 +3719,10 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
@@ -3537,16 +3749,16 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
@@ -3570,8 +3782,13 @@
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q1064344 wd:P1056 wd:Q1406 .
-</t>
+wd:Q1064344 wd:P361 wd:Q1406 .
+</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>c9d25319-bf8b-4167-aa26-172430050bbd</t>
         </is>
       </c>
     </row>
@@ -3646,9 +3863,14 @@
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q47554 wd:P1376 wd:Q54153 .
-wd:Q47554 wd:P706 wd:Q1261531 .
-</t>
+wd:Q47554 wd:P36 wd:Q54153 .
+wd:Q47554 wd:P206 wd:Q1261531 .
+</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>40eeae12-2409-475a-8ba0-9ad2983b3dda</t>
         </is>
       </c>
     </row>
@@ -3657,13 +3879,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
         <v>6</v>
@@ -3687,7 +3909,7 @@
         <v>5</v>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M42" t="n">
         <v>4</v>
@@ -3696,10 +3918,10 @@
         <v>4</v>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
         <v>4</v>
@@ -3723,11 +3945,16 @@
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q54322348 wd:P527 wd:Q16568 .
-wd:Q16568 wd:P131 wd:Q493605 .
+wd:Q54322348 wd:P131 wd:Q16568 .
+wd:Q16568 wd:P1376 wd:Q493605 .
 wd:Q16568 wd:P190 wd:Q12191 .
 wd:Q16568 wd:P190 wd:Q42622 .
 </t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>8986de6d-38b9-465b-a936-e28ebb8181f4</t>
         </is>
       </c>
     </row>
@@ -3736,19 +3963,19 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
         <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -3760,51 +3987,55 @@
         <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>2</v>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>2</v>
       </c>
       <c r="S43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
         <v>3</v>
       </c>
       <c r="V43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q87412161 wd:P3373 wd:Q95994024 .
-wd:Q87412161 wd:P31 wd:Q5 .
-</t>
+</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>2f4c689f-5b1c-422e-b365-ff99eed61a04</t>
         </is>
       </c>
     </row>
@@ -3825,7 +4056,7 @@
         <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -3837,7 +4068,7 @@
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K44" t="n">
         <v>2</v>
@@ -3858,7 +4089,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
         <v>2</v>
@@ -3867,7 +4098,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U44" t="n">
         <v>3</v>
@@ -3879,8 +4110,15 @@
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q29644512 wd:P569 "2017" .
-</t>
+wd:Q29644512 wd:P31 wd:Q154369 .
+wd:Q29644512 wd:P127 wd:Q148408 .
+wd:Q29644512 wd:P1454 wd:Q2188189 .
+</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>709fa8d7-9f13-4259-950a-2753cbef4d4d</t>
         </is>
       </c>
     </row>
@@ -3889,75 +4127,84 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
         <v>9</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
         <v>4</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K45" t="n">
         <v>7</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R45" t="n">
         <v>9</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T45" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U45" t="n">
         <v>10</v>
       </c>
       <c r="V45" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q5288565 wd:P828 wd:Q651765 .
-wd:Q5288565 wd:P2974 wd:Q258 .
-</t>
+wd:Q5288565 wd:P495 wd:Q258 .
+wd:Q5288565 wd:P366 wd:Q42329 .
+wd:Q5288565 wd:P462 wd:Q23444 .
+wd:Q7368 wd:P1535 wd:Q858177 .
+wd:Q7368 wd:P1056 wd:Q8495 .
+wd:Q5288565 wd:P361 wd:Q7368 .
+</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>35d2f25f-149d-4157-8a6a-b151d977bcca</t>
         </is>
       </c>
     </row>
@@ -3966,13 +4213,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
         <v>3</v>
@@ -3996,19 +4243,19 @@
         <v>3</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="n">
         <v>3</v>
@@ -4032,10 +4279,15 @@
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q92560 wd:P31 wd:Q231302 .
 wd:Q92560 wd:P287 wd:Q2061122 .
 wd:Q92560 wd:P449 wd:Q734663 .
-</t>
+wd:Q92560 wd:P2360 wd:Q231302 .
+</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>8e3d43cf-286c-45d3-b7f4-956781f15774</t>
         </is>
       </c>
     </row>
@@ -4056,19 +4308,19 @@
         <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
         <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
         <v>3</v>
@@ -4089,29 +4341,37 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
         <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U47" t="n">
         <v>4</v>
       </c>
       <c r="V47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q18036732 wd:P276 wd:Q753805 .
-</t>
+@prefix wdt: &lt;http://www.wikidata.org/prop/direct/&gt; .
+wd:Q18036732 wdt:P31 wd:Q7187 .
+wd:Q18036732 wdt:P706 wd:Q753805 .
+wd:Q753805 wdt:P279 wd:Q186380 .
+</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>a48e1ae1-1581-4a2b-9fe8-57253c74c62e</t>
         </is>
       </c>
     </row>
@@ -4120,74 +4380,81 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
         <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
         <v>2</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
         <v>2</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R48" t="n">
         <v>2</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U48" t="n">
         <v>3</v>
       </c>
       <c r="V48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q977911 wd:P47 wd:Q979352 .
-</t>
+wd:Q977911 wd:P131 wd:Q112686 .
+wd:Q979352 wd:P131 wd:Q112686 .
+</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>b0867fe3-c6c3-4048-8560-f753a5a89a49</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4469,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
         <v>6</v>
@@ -4211,62 +4478,67 @@
         <v>4</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
         <v>2</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K49" t="n">
         <v>6</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R49" t="n">
         <v>6</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U49" t="n">
         <v>7</v>
       </c>
       <c r="V49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q173071 wd:P541 wd:Q19546 .
-wd:Q170386 wd:P541 wd:Q19546 .
-wd:Q19546 wd:P541 wd:Q173071 .
-wd:Q19546 wd:P541 wd:Q170386 .
-</t>
+wd:Q173071 wd:P1906 wd:Q19546 .
+wd:Q173071 wd:P3342 wd:Q5 .
+wd:Q4546576 wd:P2522 wd:Q170386 .
+wd:Q4546576 wd:P1366 wd:Q1358726 .
+</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>6dd36f93-f16e-46b0-9672-21238494de0b</t>
         </is>
       </c>
     </row>
@@ -4275,13 +4547,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
         <v>3</v>
@@ -4305,13 +4577,13 @@
         <v>3</v>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -4341,10 +4613,15 @@
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
+wd:Q2822458 wd:P361 wd:Q1140115 .
+wd:Q2822458 wd:P127 wd:Q4285526 .
 wd:Q2822458 wd:P131 wd:Q649 .
-wd:Q2822458 wd:P1075 wd:Q4285526 .
-wd:Q2822458 wd:P361 wd:Q1140115 .
-</t>
+</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>1bb53ca6-7799-4319-83ea-761d2e7d262f</t>
         </is>
       </c>
     </row>
@@ -4353,13 +4630,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -4383,19 +4660,19 @@
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
@@ -4419,8 +4696,13 @@
         <is>
           <t xml:space="preserve">
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
-wd:Q2362697 wd:P556 wd:Q503601 .
-</t>
+wd:Q2362697 wd:P361 wd:Q503601 .
+</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>30b29a87-c819-42d2-9d1c-6ff3dabc2c02</t>
         </is>
       </c>
     </row>
